--- a/src/attributions/attributions_ig_traj_468.xlsx
+++ b/src/attributions/attributions_ig_traj_468.xlsx
@@ -999,49 +999,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.02545943312554834</v>
+        <v>-0.2252384655505475</v>
       </c>
       <c r="B2" t="n">
-        <v>0.08475228455900062</v>
+        <v>0.5421834257294695</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01206407644570337</v>
+        <v>-0.2114995663085163</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03844724147743023</v>
+        <v>-0.2392215576445037</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1417181812301576</v>
+        <v>1.134117081747348</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.03757402201146318</v>
+        <v>-0.3507354999624888</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1053,19 +1053,19 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02663566947218833</v>
+        <v>0.03824957720748594</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09926810399453639</v>
+        <v>0.1018678386199441</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1012940164398904</v>
+        <v>-0.02996377374906348</v>
       </c>
       <c r="X2" t="n">
         <v>-0</v>
@@ -1080,37 +1080,37 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04770441481635852</v>
+        <v>0.03099853769979909</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1394503738523917</v>
+        <v>0.1090731367776103</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.02303971740465841</v>
+        <v>0.04563605746758677</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.01431110965937826</v>
+        <v>-0.008263404705905</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04274326335583015</v>
+        <v>0.2241225029960055</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,52 +1119,52 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.03545734937928139</v>
+        <v>0.0617782951945795</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.08970689936867329</v>
+        <v>-0.1021689211212089</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1733921020432</v>
+        <v>1.186059630490765</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3271680839133949</v>
+        <v>-0.2470660323862009</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.04292210025641571</v>
+        <v>-0.2268758451331835</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.05229658503043825</v>
+        <v>-0.003645925568847837</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,40 +1173,40 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.140868161204805</v>
+        <v>-0.1034211115438751</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.03915377756486328</v>
+        <v>-0.03075771804063882</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.1038200641909091</v>
+        <v>0.05218837114764592</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.02522419326592908</v>
+        <v>0.1879739690171962</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
@@ -1215,37 +1215,37 @@
         <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.06096896643957952</v>
+        <v>0.06469093751601525</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1324208659844935</v>
+        <v>0.8048367122191861</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1350886715370666</v>
+        <v>-0.1532944633990968</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.00947553672988293</v>
+        <v>0.1129826772567878</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.05409782398927396</v>
+        <v>-0.4980910670437758</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
@@ -1254,52 +1254,52 @@
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.02180555613166997</v>
+        <v>0.08646875122725971</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.02607928067486253</v>
+        <v>-0.02926155114736329</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01163973146207808</v>
+        <v>-0.4962879344051995</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.08922309975203553</v>
+        <v>-0.0456129838200452</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.003497493003951163</v>
+        <v>0.07467848598906078</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.07339841403671739</v>
+        <v>-0.4967565100849667</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
@@ -1308,10 +1308,10 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01567919905981883</v>
+        <v>0.02675275435140399</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.004550056061425393</v>
+        <v>0.04292452555202645</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1037807712386701</v>
+        <v>-0.4104296335337668</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,34 +1335,34 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.009649680454666519</v>
+        <v>-0.002441709946316185</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.0005880639089663686</v>
+        <v>0.03942719817150194</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01390530274704697</v>
+        <v>-0.26025935189114</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.02139385724320211</v>
+        <v>-0.1358573967440833</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.005375943261103972</v>
+        <v>0.1903692168809126</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.09182911846435894</v>
+        <v>0.3306751317123661</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
@@ -1389,40 +1389,40 @@
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.02990306134063583</v>
+        <v>-0.06005387111722223</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.02696133812250583</v>
+        <v>-0.02687163885741373</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.01506627199424617</v>
+        <v>-0.3212442944116606</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01194390400960646</v>
+        <v>-0.02374876550122442</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>-0</v>
@@ -1431,19 +1431,19 @@
         <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.02072167574920233</v>
+        <v>0.008403126222373646</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.0897686801880342</v>
+        <v>-0.1792380391957079</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.02573392063007406</v>
+        <v>-0.03108592338140359</v>
       </c>
       <c r="ET2" t="n">
         <v>-0</v>
@@ -1455,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.001759026364267314</v>
+        <v>0.1094200385949967</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.07829367987588727</v>
+        <v>-0.5804199174730785</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.05067973534260083</v>
+        <v>0.01070528482501024</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
@@ -1485,10 +1485,10 @@
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.03831791108791755</v>
+        <v>-0.004553866832449394</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.02374318342715216</v>
+        <v>-0.2436476432525598</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,7 +1497,7 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.03472530361125099</v>
+        <v>0.1917030441582319</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1506,43 +1506,43 @@
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0.002149940014420108</v>
+        <v>0.09259679455946225</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.02012057084164451</v>
+        <v>-0.01217965885802418</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.005751790828782861</v>
+        <v>0.02179951510105319</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0.03852420893188967</v>
+        <v>0.1240885233807224</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.02712994278049733</v>
+        <v>-0.3781818749444961</v>
       </c>
       <c r="GA2" t="n">
         <v>-0</v>
@@ -1554,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,33 +1563,33 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02150109099733667</v>
+        <v>0.03779775485388845</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01332675001760003</v>
+        <v>0.04323032146108585</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2349286709760998</v>
+        <v>0.07478220081051369</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -1598,49 +1598,49 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.09325655321280467</v>
+        <v>-0.2546034641862771</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03248461548490431</v>
+        <v>0.1012756101403541</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2631672348458176</v>
+        <v>0.1713964960139077</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02789666852686421</v>
+        <v>-0.01983912177726192</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.03741209912366455</v>
+        <v>0.01669108727288404</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05164417648099637</v>
+        <v>-0.05539675390010802</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1652,34 +1652,34 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.05498922332031031</v>
+        <v>-0.06851906415194539</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.02195093400269879</v>
+        <v>-0.1095412986543235</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.08960324497734247</v>
+        <v>0.07245934123737555</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.04698866097859414</v>
+        <v>-0.1155121632897427</v>
       </c>
       <c r="AM3" t="n">
         <v>-0</v>
@@ -1688,52 +1688,52 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.03297077097491873</v>
+        <v>-0.1467719163510566</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.04548226544923707</v>
+        <v>-0.04866530371098723</v>
       </c>
       <c r="AR3" t="n">
         <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.4106728816587939</v>
+        <v>-0.4723633682590372</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.06416710946917481</v>
+        <v>-0.02240834566733852</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2787932248820009</v>
+        <v>-0.01822219277216371</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.002540672778918682</v>
+        <v>0.00219874266104773</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,13 +1742,13 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01219271992362592</v>
+        <v>0.01065990721798959</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.07923462919531171</v>
+        <v>0.08233512617994082</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1120236873731606</v>
+        <v>0.1755865067666895</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
@@ -1769,13 +1769,13 @@
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.04193010919793981</v>
+        <v>-0.0825094847420071</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0414927478600727</v>
+        <v>-0.06170982207967021</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1787,52 +1787,52 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.2296989776042901</v>
+        <v>-0.3477446085519859</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-2.315419311476246e-05</v>
+        <v>-0.02774668953715486</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.171626656171827</v>
+        <v>-0.009878265715880191</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.07676726341508522</v>
+        <v>0.2591660600284186</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01602384548544271</v>
+        <v>0.003357410751451914</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.114729943853453</v>
+        <v>-0.06594449576360642</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,22 +1841,22 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001521817099234331</v>
+        <v>0.1553469035241472</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.07521822895854757</v>
+        <v>0.05501839377412449</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.02604506290058145</v>
+        <v>-0.008839212119263426</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
@@ -1865,25 +1865,25 @@
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.08993557603033714</v>
+        <v>0.2714780805742437</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01693266851317075</v>
+        <v>-0.002780082574254513</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.1081593640767389</v>
+        <v>-0.06744542136076756</v>
       </c>
       <c r="DC3" t="n">
         <v>-0</v>
@@ -1895,49 +1895,49 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.192521231183317</v>
+        <v>0.0260216696352379</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.02940600386977735</v>
+        <v>0.02437624601338348</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.07781021898020367</v>
+        <v>-0.004886077630951228</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.02184233141500899</v>
+        <v>0.1774759741591244</v>
       </c>
       <c r="DP3" t="n">
         <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01632661419545361</v>
+        <v>0.09022267922728297</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.07012413698133649</v>
+        <v>-0.07958087054720665</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1949,22 +1949,22 @@
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.1258395996062912</v>
+        <v>-0.1695005561432071</v>
       </c>
       <c r="DY3" t="n">
         <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.03235059893502919</v>
+        <v>0.1173757402763263</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.04455370771825214</v>
+        <v>0.1023294569706926</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
@@ -1973,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.04870339398592579</v>
+        <v>0.2358196421198839</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.007517611362527499</v>
+        <v>-0.016082781810357</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0.08051830749969364</v>
+        <v>-0.04808383515190228</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.04598418442684712</v>
+        <v>0.1717813453362447</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
@@ -2012,40 +2012,40 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03086030729847248</v>
+        <v>-0.0467439674167518</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.05571761697093224</v>
+        <v>0.001571231443411164</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.09956868481526514</v>
+        <v>0.28232336923881</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.04970471050563261</v>
+        <v>-0.005312540038038601</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0.1196287768493677</v>
+        <v>-0.05190642783761649</v>
       </c>
       <c r="FE3" t="n">
         <v>0</v>
@@ -2054,37 +2054,37 @@
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.07786933482385071</v>
+        <v>0.001582352244331709</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.0462637701221587</v>
+        <v>0.1129035580776251</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0.03802589593800818</v>
+        <v>0.0359896833992129</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.02050018587926423</v>
+        <v>0.05244561686798255</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01858683657621232</v>
+        <v>0.01196537753156663</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.09124389771119898</v>
+        <v>0.05100938995771101</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
         <v>-0</v>
@@ -2111,10 +2111,10 @@
         <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.01710165600081365</v>
+        <v>0.2800287267889914</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.08449163924702577</v>
+        <v>0.09190589461918942</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2706,19 +2706,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7415654654196994</v>
+        <v>0.1969414783448424</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4139755518632369</v>
+        <v>-0.2818956436674604</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06761904165720421</v>
+        <v>-0.01403159993879113</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2733,19 +2733,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7186651964045164</v>
+        <v>0.2452361111820789</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.517846788521574</v>
+        <v>-0.5122138449087695</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2072200141014284</v>
+        <v>-0.05661970607546526</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2757,55 +2757,55 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1873490471270572</v>
+        <v>0.07342695046598052</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1388234156118392</v>
+        <v>-0.05621705924572406</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1199595635140566</v>
+        <v>-0.127008075982938</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2474065091305448</v>
+        <v>-0.04543883945825503</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0690584192057808</v>
+        <v>-0.07157770639964588</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.009717749731409013</v>
+        <v>-0.0590579894117807</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,25 +2814,25 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0994016067302399</v>
+        <v>0.07657020281041164</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0861664805606316</v>
+        <v>-0.08352635671470561</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08336999453779743</v>
+        <v>0.03067634802647722</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2844,43 +2844,43 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.050118355951266</v>
+        <v>0.3442897110481598</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1301856408988462</v>
+        <v>-0.2516386182652153</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.192157168564117</v>
+        <v>-0.3543089346732625</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1158057328563714</v>
+        <v>-0.02071774825431641</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1259112819795501</v>
+        <v>-0.03868412983580982</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.2931200167393685</v>
+        <v>0.009529203387614074</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1983600446021152</v>
+        <v>0.002255783775352874</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.2049831313944083</v>
+        <v>0.03795737648824286</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1014718295710798</v>
+        <v>-0.01246980323740546</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,19 +2925,19 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.5537499689634907</v>
+        <v>0.2205974630081577</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.06272050611578527</v>
+        <v>-0.1321605121701525</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.009842638143925914</v>
+        <v>-0.1113445168471864</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2946,25 +2946,25 @@
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.2432031145287149</v>
+        <v>-0.08926871736926062</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.08284066078889779</v>
+        <v>0.1923688851963125</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.05687487219012666</v>
+        <v>0.02477175678683458</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
@@ -2973,22 +2973,22 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01352773777370735</v>
+        <v>-0.01254263619314203</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.2025194129659655</v>
+        <v>0.2632994937007869</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.07879002120018806</v>
+        <v>0.09665294241393296</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -3000,25 +3000,25 @@
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.2002194691151225</v>
+        <v>-0.08538317067568192</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.148312899284254</v>
+        <v>0.211607988538835</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.04662228871039062</v>
+        <v>0.03086815665824295</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3033,46 +3033,46 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.04375468272918044</v>
+        <v>-0.02569152428978399</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.1711515059222271</v>
+        <v>0.1031170232865831</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05412388696244154</v>
+        <v>-0.02956395052203207</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1327011861007172</v>
+        <v>-0.05944815121520892</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.05694873803101076</v>
+        <v>0.09892020756999505</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.1192397266369812</v>
+        <v>-0.01861257831127795</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
@@ -3087,76 +3087,76 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01572755271202928</v>
+        <v>0.04541459194490489</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.009472864672750936</v>
+        <v>0.09127489626753771</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.08161022271631488</v>
+        <v>-0.04251035944122372</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1079105449572693</v>
+        <v>-0.03876073143672387</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.07469766010072809</v>
+        <v>0.1470283631819014</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.08445627512653789</v>
+        <v>0.0377654281408128</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.2004255136086093</v>
+        <v>-0.02820115192941449</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1650661736148906</v>
+        <v>-0.1389212120115884</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.09700102471807839</v>
+        <v>-0.0408319544181205</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.2053438917146123</v>
+        <v>-0.09385126433474629</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.1342041453962133</v>
+        <v>0.2282873439225081</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.05237483026278682</v>
+        <v>0.0117549457015335</v>
       </c>
       <c r="FC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
@@ -3192,22 +3192,22 @@
         <v>0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.06562547154730013</v>
+        <v>-0.0549325917862994</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.1154312095517205</v>
+        <v>0.102187542848444</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.009508612099894016</v>
+        <v>0.01929004914204186</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3219,22 +3219,22 @@
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.03060870914009605</v>
+        <v>0.04766078158010321</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.08506280759072983</v>
+        <v>0.2107732367076104</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.05812874243791458</v>
+        <v>-0.09265514503924729</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,28 +3246,28 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.05339054911747536</v>
+        <v>-0.07206707314860678</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.01026776338326901</v>
+        <v>0.1716140760089523</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3278,52 +3278,52 @@
         <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.8257549200977765</v>
+        <v>-0.159644711072988</v>
       </c>
       <c r="C6" t="n">
         <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4327317699562636</v>
+        <v>0.1288008388879004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.007082802895917907</v>
+        <v>-0.01401279731475981</v>
       </c>
       <c r="F6" t="n">
         <v>-0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005493804677773622</v>
+        <v>0.0124190709542016</v>
       </c>
       <c r="I6" t="n">
         <v>-0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7083002401394107</v>
+        <v>-0.2121977400305644</v>
       </c>
       <c r="L6" t="n">
         <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6623413133900374</v>
+        <v>0.2934962956450785</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1405543195454075</v>
+        <v>0.06979249399936241</v>
       </c>
       <c r="O6" t="n">
         <v>-0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0186950767212628</v>
+        <v>-0.001756285284228787</v>
       </c>
       <c r="R6" t="n">
         <v>-0</v>
@@ -3332,43 +3332,43 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1757971584444062</v>
+        <v>-0.1057857693226234</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0856217408298575</v>
+        <v>0.07590248565554461</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09816438517617047</v>
+        <v>0.07454626159944741</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02062011628508615</v>
+        <v>0.004440561028437585</v>
       </c>
       <c r="AA6" t="n">
         <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3441470395878349</v>
+        <v>0.06965259777790771</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.08737229249186468</v>
+        <v>0.1212195423087494</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.06739519706546822</v>
+        <v>0.07103444698105559</v>
       </c>
       <c r="AG6" t="n">
         <v>-0</v>
@@ -3377,25 +3377,25 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.008022177548023644</v>
+        <v>-0.01398366976584523</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.1312140521670884</v>
+        <v>-0.08013725021155102</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07966060419873078</v>
+        <v>0.02959350273982078</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.004665896933825487</v>
+        <v>-0.1204397486685578</v>
       </c>
       <c r="AP6" t="n">
         <v>-0</v>
@@ -3404,52 +3404,52 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.04499953229245628</v>
+        <v>-0.007688468964689188</v>
       </c>
       <c r="AS6" t="n">
         <v>-0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.059117498017009</v>
+        <v>-0.3895088544584434</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2259094241868461</v>
+        <v>0.1318214032381688</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1427971865711374</v>
+        <v>0.2072782597991226</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.02308704685605173</v>
+        <v>0.03904820608112277</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1600744848165692</v>
+        <v>0.09751921220297745</v>
       </c>
       <c r="BE6" t="n">
         <v>-0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1231643140026819</v>
+        <v>0.03518042204411141</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.2734582147211752</v>
+        <v>0.1828516395413387</v>
       </c>
       <c r="BH6" t="n">
         <v>-0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.02240394220392726</v>
+        <v>0.006022823092848499</v>
       </c>
       <c r="BK6" t="n">
         <v>-0</v>
@@ -3467,79 +3467,79 @@
         <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1017898693351529</v>
+        <v>0.06980951810384441</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.125340569637715</v>
+        <v>0.06082762454840589</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.1411752336613672</v>
+        <v>0.08197300252224664</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01666570678915437</v>
+        <v>0.02285002960615089</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.5271845562670818</v>
+        <v>-0.2174059949954249</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.08884208931354308</v>
+        <v>0.1758190310501222</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.04738505255597852</v>
+        <v>0.1097839128623633</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.04153537094908415</v>
+        <v>0.06601016649384814</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.2437092417737923</v>
+        <v>0.1072561213752559</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.06410578260183947</v>
+        <v>-0.07730595001146683</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.06906480895784971</v>
+        <v>-0.00630207331010517</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.02762947783878146</v>
+        <v>0.05093879419478681</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
@@ -3548,16 +3548,16 @@
         <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0258732926586401</v>
+        <v>0.05829325008739613</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.1283588660385905</v>
+        <v>-0.179588904077594</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0106645090225752</v>
+        <v>-0.2804602170380256</v>
       </c>
       <c r="CR6" t="n">
         <v>-0</v>
@@ -3566,25 +3566,25 @@
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.1216883447221997</v>
+        <v>-0.04085098721857964</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.1872062132142719</v>
+        <v>0.1027977876277184</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.1311011254837149</v>
+        <v>-0.0766294852532152</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0827395907722739</v>
+        <v>-0.01207346806870468</v>
       </c>
       <c r="DA6" t="n">
         <v>-0</v>
@@ -3593,52 +3593,52 @@
         <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.02281987611696388</v>
+        <v>0.02246493194699369</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.2431486692263554</v>
+        <v>0.06331238114719945</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.1026679114335289</v>
+        <v>-0.0270274489027057</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.04312810220318534</v>
+        <v>0.01547612756938611</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.008546581458961661</v>
+        <v>0.03927936419617867</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.2176390559532849</v>
+        <v>-0.01698407805764662</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.01053410083434608</v>
+        <v>-0.1369212551425966</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.1982980543344964</v>
+        <v>0.07863352542401972</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.09024173453954455</v>
+        <v>0.01230817846276576</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,16 +3656,16 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.005066150369696195</v>
+        <v>-0.07584879870146534</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.06200524694035472</v>
+        <v>-0.06204750575799352</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2243227501254805</v>
+        <v>0.01280591418130358</v>
       </c>
       <c r="EB6" t="n">
         <v>-0</v>
@@ -3674,79 +3674,79 @@
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.005275313565265847</v>
+        <v>-0.006015188253306615</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.08520260288134333</v>
+        <v>0.03704036781278694</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.1324916862440012</v>
+        <v>0.05255401666495062</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.06302840293927302</v>
+        <v>-0.06838904596945897</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.007912228002495802</v>
+        <v>0.06828172127243567</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.1480740836833224</v>
+        <v>0.0297466141146683</v>
       </c>
       <c r="EQ6" t="n">
         <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.1708330743345714</v>
+        <v>-0.01677913425296517</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.04851003958488581</v>
+        <v>0.07963604870174028</v>
       </c>
       <c r="ET6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.2286283557749093</v>
+        <v>-0.0007342749633478399</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.2040533151386228</v>
+        <v>0.1106139253803609</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0.1106280412884404</v>
+        <v>-0.119576897553551</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.03892722833287867</v>
+        <v>-0.02022090036313352</v>
       </c>
       <c r="FC6" t="n">
         <v>0</v>
@@ -3755,52 +3755,52 @@
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.02409375713589483</v>
+        <v>0.04037257420195176</v>
       </c>
       <c r="FF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG6" t="n">
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.08707795247122427</v>
+        <v>0.1343173176466229</v>
       </c>
       <c r="FI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.1054295159618057</v>
+        <v>0.07396765171368247</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.1216282144947392</v>
+        <v>-0.07145109846323049</v>
       </c>
       <c r="FL6" t="n">
         <v>0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0.03600952014479839</v>
+        <v>0.06019628796808753</v>
       </c>
       <c r="FO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP6" t="n">
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.03195720039283426</v>
+        <v>-0.2253189983692936</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.1048687528826066</v>
+        <v>-0.2258508356561996</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.09092032746104674</v>
+        <v>0.1214433951290303</v>
       </c>
       <c r="FU6" t="n">
         <v>0</v>
@@ -3809,22 +3809,22 @@
         <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.04341182893987094</v>
+        <v>-0.06327151408166543</v>
       </c>
       <c r="FX6" t="n">
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.1278051706775719</v>
+        <v>0.08790446501111392</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.1221427682238812</v>
+        <v>-0.06735575364469691</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>-0.04270931742934498</v>
+        <v>0.04439014194280766</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5102989764692988</v>
+        <v>0.3088933219091232</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2194621023235412</v>
+        <v>-0.1500246562193859</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1166055119921297</v>
+        <v>0.1040528758196939</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6054566815441248</v>
+        <v>0.4625729822909395</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2788060831825133</v>
+        <v>-0.3077366385666184</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.167194849402978</v>
+        <v>0.1057340348183571</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,76 +3895,76 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1556461415398622</v>
+        <v>0.1367091104878355</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.02489008670392922</v>
+        <v>-0.007133448101227697</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08723094964562661</v>
+        <v>-0.04521601569315559</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0721278887954012</v>
+        <v>0.01264543179721725</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.03942499739604773</v>
+        <v>-0.1780578574275435</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.04261945969574099</v>
+        <v>-0.01439525017638013</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03157426666893891</v>
+        <v>0.1049260596827356</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1164942815988829</v>
+        <v>-0.1084752705728857</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07406795265869953</v>
+        <v>0.05524733556022784</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3979,46 +3979,46 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5114140491531739</v>
+        <v>0.4416904643046024</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.138512847052726</v>
+        <v>-0.183541397738686</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1573909223435526</v>
+        <v>-0.1900278090765002</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.08798770937791335</v>
+        <v>-0.02739900583904701</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.06082904923574089</v>
+        <v>-0.07161948264401972</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1682206507724124</v>
+        <v>0.04362181643674687</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,28 +4027,28 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05640667539091036</v>
+        <v>-0.0006106157361179923</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.08060139986028869</v>
+        <v>-0.01699648684301616</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1764728220004832</v>
+        <v>0.04142951049347211</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
@@ -4060,127 +4060,127 @@
         <v>-0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2602607824310388</v>
+        <v>0.334452548057417</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.02046832831794853</v>
+        <v>-0.06806207232832644</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1000050768756721</v>
+        <v>0.04248246484877852</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1525607633261377</v>
+        <v>-0.1343838071641311</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05100015523759778</v>
+        <v>0.1296076792996788</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01041755188067351</v>
+        <v>-0.07565453718123048</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.007369306370719469</v>
+        <v>-0.1225243305297224</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.09938263800383386</v>
+        <v>0.2311951064495154</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1600088460994262</v>
+        <v>0.003735433709485196</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1479253317283559</v>
+        <v>-0.12695453056817</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.08551330436152459</v>
+        <v>0.1273224164465884</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.006043757091433855</v>
+        <v>-0.074311650213872</v>
       </c>
       <c r="DA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.06603043526724889</v>
+        <v>-0.1256463330430549</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.06520270753912694</v>
+        <v>0.05658914509415087</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.003796856746068803</v>
+        <v>-0.05431876423168459</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,25 +4189,25 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.03671527431894548</v>
+        <v>-0.08419521808501969</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1713105285000283</v>
+        <v>-0.001521379030015437</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.08996991639410924</v>
+        <v>-0.05062443624579752</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
@@ -4216,7 +4216,7 @@
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,16 +4225,16 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.09588283663988595</v>
+        <v>-0.02893608449144823</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.03257435736004852</v>
+        <v>-0.1453791763835315</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.02179846432680126</v>
+        <v>-0.1584913401149279</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
@@ -4243,163 +4243,163 @@
         <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1797171608491478</v>
+        <v>-0.09099735334176487</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.09987143308998736</v>
+        <v>0.1096273480962281</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.112965752637435</v>
+        <v>-0.03036858496635217</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1073599093000863</v>
+        <v>-0.08015810668909877</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09299935471426404</v>
+        <v>0.01230433437526867</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01933606421302718</v>
+        <v>-0.009303479961372646</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1458470104202151</v>
+        <v>-0.1662225631695818</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.06539380666436378</v>
+        <v>0.1489777429499116</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.01294094205858187</v>
+        <v>-0.07463043276392438</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.004511636933839621</v>
+        <v>0.1077065981705103</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1300280946652952</v>
+        <v>0.1153432582541856</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.03621182368369379</v>
+        <v>0.02620273710292534</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.06439500445683233</v>
+        <v>-0.06866161636718822</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.02716953438506473</v>
+        <v>0.03747365070365501</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.0527331209051207</v>
+        <v>0.08913958020493816</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01133754080714991</v>
+        <v>-0.1483175784386175</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.05420837652457094</v>
+        <v>0.08972919069032903</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,46 +4416,46 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3943193651665309</v>
+        <v>0.3595602377760884</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1306554319646084</v>
+        <v>-0.1381787735804865</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08579629740681993</v>
+        <v>0.03979615604814401</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.445272482811555</v>
+        <v>0.5666029184939742</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1891826052309578</v>
+        <v>-0.3349247163472966</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1445939196873666</v>
+        <v>-0.02450583107230074</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8" t="n">
         <v>-0</v>
@@ -4464,76 +4464,76 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1067407204474842</v>
+        <v>0.1323298258723685</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.008207769713851355</v>
+        <v>-0.01276700204604569</v>
       </c>
       <c r="W8" t="n">
-        <v>0.09626117867599016</v>
+        <v>-0.0817662899267647</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.06470347751991484</v>
+        <v>0.03968855106123979</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0126947240754478</v>
+        <v>-0.237816895179333</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00135924048493019</v>
+        <v>-0.0390837299998623</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.006513334005186236</v>
+        <v>0.1318390687229072</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.06876660147078217</v>
+        <v>-0.03708078151191926</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.08868498685911561</v>
+        <v>0.0114061349997123</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -4542,25 +4542,25 @@
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3974313951788611</v>
+        <v>0.5313994336213396</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.05875759585893685</v>
+        <v>-0.2107247088955785</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1261802599623959</v>
+        <v>-0.2933217155738391</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
@@ -4569,25 +4569,25 @@
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07541890470617509</v>
+        <v>-0.04882237544968192</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.05500517959038867</v>
+        <v>-0.02052767184184011</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.0996567080781421</v>
+        <v>0.03008136830540881</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4596,28 +4596,28 @@
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.06290811811969925</v>
+        <v>0.06584515470341257</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04111741823615669</v>
+        <v>-0.006837337323163441</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1986581959611216</v>
+        <v>0.07631489830202992</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
@@ -4629,52 +4629,52 @@
         <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1899339092448068</v>
+        <v>0.3619373392165498</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.004809485336731082</v>
+        <v>-0.09557357063133021</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.1017968932710338</v>
+        <v>-0.06391889839346562</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.112308788417775</v>
+        <v>-0.1504606280967506</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0235409069025973</v>
+        <v>0.1275434726678275</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.005012124142028401</v>
+        <v>-0.0104155698192804</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,124 +4686,124 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.03910669363301192</v>
+        <v>-0.1636729625052191</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.08975225574420045</v>
+        <v>0.2328690935719752</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.1324498786093077</v>
+        <v>0.06150961538515035</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.1020703846163088</v>
+        <v>-0.133813219057754</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.04606844717113913</v>
+        <v>0.141515064391827</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0009112587841436621</v>
+        <v>-0.02319512250103313</v>
       </c>
       <c r="DA8" t="n">
         <v>-0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.06939568489784952</v>
+        <v>-0.06155888124128518</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.08903271663747307</v>
+        <v>0.0749687088618665</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.004277643548448032</v>
+        <v>-0.1466395151497164</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.04571676209750867</v>
+        <v>-0.09412887406083882</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.1519378007172607</v>
+        <v>-0.001473649508215955</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.04091292482472586</v>
+        <v>-0.04938235877031954</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.100309438640209</v>
+        <v>-0.03165204828997198</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.006179942571031783</v>
+        <v>0.0218036915708876</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.05388164529719886</v>
+        <v>-0.002270415320281191</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,106 +4812,106 @@
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.1406482680113492</v>
+        <v>-0.08203383094999697</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.09113840961439969</v>
+        <v>-0.2536986245995985</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.09047147559959996</v>
+        <v>-0.02461853274267486</v>
       </c>
       <c r="EK8" t="n">
         <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.0751662120313938</v>
+        <v>-0.05639351045874579</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.05795202620691003</v>
+        <v>-0.005233375556905545</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.01621821835522816</v>
+        <v>-0.02824641572180296</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.1047399926588306</v>
+        <v>-0.1689811473457714</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.02518550666891668</v>
+        <v>0.154578218502218</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01265590360925122</v>
+        <v>-0.02328059190443243</v>
       </c>
       <c r="FC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.05330665274666341</v>
+        <v>0.1169487870749063</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.06301711080769461</v>
+        <v>0.1398135299394344</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.04976050259043496</v>
+        <v>0.001505498172982398</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
@@ -4926,25 +4926,25 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.0001740510436491392</v>
+        <v>-0.2220095230530129</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.0732262112101303</v>
+        <v>0.1684921130182516</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.003193916435310223</v>
+        <v>0.1546913486024719</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
@@ -4953,19 +4953,19 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.03070286867574388</v>
+        <v>-0.127705912881887</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.06625965011625637</v>
+        <v>0.06249047625357812</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
         <v>-0</v>
@@ -4974,36 +4974,36 @@
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.11788592015549</v>
+        <v>-0.6935738691686275</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5255915514286402</v>
+        <v>0.3630541064583004</v>
       </c>
       <c r="D9" t="n">
         <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2098363662124645</v>
+        <v>-0.09933909331921328</v>
       </c>
       <c r="F9" t="n">
         <v>-0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2697036595340567</v>
+        <v>-0.06051674043800829</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>-0</v>
@@ -5012,130 +5012,130 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.203036616185605</v>
+        <v>-1.147475594792585</v>
       </c>
       <c r="L9" t="n">
-        <v>0.572890430605005</v>
+        <v>0.5869600685218005</v>
       </c>
       <c r="M9" t="n">
         <v>-0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1820048881512676</v>
+        <v>-0.04177678403124931</v>
       </c>
       <c r="O9" t="n">
         <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3161891698333042</v>
+        <v>-0.04052394699232165</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1411107346628276</v>
+        <v>-0.1192529180568662</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1128543070571673</v>
+        <v>-0.1892028295170945</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.142667975347716</v>
+        <v>-0.1398222941563303</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.04185174534991038</v>
+        <v>-0.02683151929697009</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.3748898387891709</v>
+        <v>-0.07100457562358707</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0486215162122529</v>
+        <v>0.1621627766009823</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.08596728485098631</v>
+        <v>0.2665373202199844</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1700104173305432</v>
+        <v>0.2157905235048113</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.1326538028199269</v>
+        <v>-0.3214265321761702</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.1800319132563881</v>
+        <v>0.04170196243623198</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1107821089025908</v>
+        <v>-0.2614544978144883</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.06517021431962254</v>
+        <v>0.1051320808069969</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-1.02785701519028</v>
+        <v>-0.7839033192415246</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.3658661281260695</v>
+        <v>-0.02026006389442304</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.146293481411265</v>
+        <v>-0.08258197496506769</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5246792393045687</v>
+        <v>-0.05264660875432046</v>
       </c>
       <c r="BA9" t="n">
         <v>-0</v>
@@ -5144,52 +5144,52 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.423631951637741</v>
+        <v>0.1435295009817182</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.2456382378537764</v>
+        <v>0.2997249852106033</v>
       </c>
       <c r="BF9" t="n">
         <v>-0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0985668607863831</v>
+        <v>0.07812032005048976</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.09966977532764405</v>
+        <v>0.007153022500273741</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
         <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.3065824885678687</v>
+        <v>0.125633803647534</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1650897011076954</v>
+        <v>0.004368639214939911</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0113587830863912</v>
+        <v>0.04000152290149636</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.03980362028020653</v>
+        <v>0.1299154360778984</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.4077628553080349</v>
+        <v>-0.4605084881409293</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.4897908931918873</v>
+        <v>-0.007622728028340212</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.04177355118534228</v>
+        <v>-0.1410127445780365</v>
       </c>
       <c r="BZ9" t="n">
         <v>-0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.1096388314426604</v>
+        <v>-0.05912915346581207</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5225,28 +5225,28 @@
         <v>-0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.3090907840751156</v>
+        <v>0.3631404212434942</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.006707814435616705</v>
+        <v>-0.1244019920072797</v>
       </c>
       <c r="CG9" t="n">
         <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.08840619449034394</v>
+        <v>0.0432989761292171</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0.1657705968674665</v>
+        <v>-0.04800446894605241</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
@@ -5255,52 +5255,52 @@
         <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.1095181034653907</v>
+        <v>0.2709917410354341</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.08469395128561909</v>
+        <v>-0.08115056595554147</v>
       </c>
       <c r="CP9" t="n">
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.05181514063959886</v>
+        <v>-0.1677984196689767</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0.189684140419285</v>
+        <v>-0.05807662910680334</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.2957267553532594</v>
+        <v>0.3683806025365518</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.04288566739667386</v>
+        <v>-0.1226407039027079</v>
       </c>
       <c r="CY9" t="n">
         <v>-0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.1579794294904072</v>
+        <v>0.04107928120666245</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0.1426782260366452</v>
+        <v>-0.03076768379147816</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>-0</v>
@@ -5309,103 +5309,103 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.2994805425027273</v>
+        <v>0.07746187840899746</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001885566708703056</v>
+        <v>-0.170283727536539</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1049780757630098</v>
+        <v>0.5187421469659175</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.09481462778908142</v>
+        <v>0.007247420633949995</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0310238841161953</v>
+        <v>0.1245321281495486</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.1695692231994335</v>
+        <v>-0.06092318786423388</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.08379285949150594</v>
+        <v>0.06565042447304613</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0.04066907492119163</v>
+        <v>-0.2056347809356663</v>
       </c>
       <c r="DU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="n">
         <v>-0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.4065538194024412</v>
+        <v>0.1698628657787656</v>
       </c>
       <c r="DY9" t="n">
-        <v>-0.008415674542576745</v>
+        <v>0.0034887465861237</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.08247086387612239</v>
+        <v>0.1176927483349115</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.03610306731802416</v>
+        <v>0.1668355488846034</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.1816570585294598</v>
+        <v>0.266804877332487</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.006468245605728418</v>
+        <v>0.04621749925253216</v>
       </c>
       <c r="EI9" t="n">
         <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.002676883710973253</v>
+        <v>-0.01617428871158466</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0.183982479078011</v>
+        <v>0.0359223673781086</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.2097248546743879</v>
+        <v>0.3279052006537185</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0966767603149668</v>
+        <v>-0.002791026922267563</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.2706104772004796</v>
+        <v>-0.06107293393692784</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0.1424791326676946</v>
+        <v>0.06939370861216387</v>
       </c>
       <c r="EV9" t="n">
         <v>-0</v>
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.2898156667977808</v>
+        <v>0.4339544254020502</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.01852631323689344</v>
+        <v>-0.1121277081418562</v>
       </c>
       <c r="FA9" t="n">
         <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.1142302591828582</v>
+        <v>0.01685058082989949</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0.1643308079825965</v>
+        <v>-0.03223021331493949</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>0</v>
@@ -5471,99 +5471,99 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0506586688569906</v>
+        <v>-0.1159249810947791</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0.06519405922638997</v>
+        <v>-0.2512536857314855</v>
       </c>
       <c r="FJ9" t="n">
         <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.1273491079634385</v>
+        <v>-0.1214924849911168</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.04050806901338474</v>
+        <v>0.1912742502455401</v>
       </c>
       <c r="FN9" t="n">
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.07928288301580085</v>
+        <v>0.2354618098848423</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0.2713065346555488</v>
+        <v>0.06578069777744337</v>
       </c>
       <c r="FS9" t="n">
         <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.07293272832706796</v>
+        <v>-0.07129976614382269</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.01209100598128424</v>
+        <v>-0.008421811195240035</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
         <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.2061241061942416</v>
+        <v>0.3176909501774761</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.126900114773942</v>
+        <v>0.176137487148789</v>
       </c>
       <c r="GB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.07351966385547108</v>
+        <v>0.2020525318139168</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2321708712366192</v>
+        <v>0.02482909894688461</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.02628603503066204</v>
+        <v>-0.007859148999830486</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07114207376084189</v>
+        <v>-0.006534445578011855</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5578,22 +5578,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.195151464644812</v>
+        <v>0.0315268999024402</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.01908022374135512</v>
+        <v>-0.01080232765696357</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.122989645743658</v>
+        <v>-0.01103190873716135</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5608,16 +5608,16 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04723094566446503</v>
+        <v>0.007368041371419607</v>
       </c>
       <c r="U10" t="n">
-        <v>0.006454050297383187</v>
+        <v>0.0004419413400104129</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.003664466746930031</v>
+        <v>0.008278993292726914</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
@@ -5626,7 +5626,7 @@
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -5635,52 +5635,52 @@
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06764449039264343</v>
+        <v>-0.002883463087869684</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.004979437173426234</v>
+        <v>-0.01002318981646305</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01493361457010906</v>
+        <v>-0.00825768495865419</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.04472650859249754</v>
+        <v>0.01542460550531623</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001826661312081346</v>
+        <v>-0.002099982325499866</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.001892355429161138</v>
+        <v>0.01449159709578462</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,25 +5689,25 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1965791177274343</v>
+        <v>0.03032450172576844</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0004164947430481439</v>
+        <v>-0.002507836223463219</v>
       </c>
       <c r="AW10" t="n">
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.01321122691897829</v>
+        <v>-0.004508781379816105</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,19 +5716,19 @@
         <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04614436024833572</v>
+        <v>-0.003851828117671745</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.02864260911938168</v>
+        <v>-0.004488573413329792</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.07586934454187137</v>
+        <v>-0.0118143792458435</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>-0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.01146684363670128</v>
+        <v>-1.262982972243639e-05</v>
       </c>
       <c r="BN10" t="n">
-        <v>-0.01502777594317167</v>
+        <v>-0.002820802928537449</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02897458204047512</v>
+        <v>0.006349928044224475</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,19 +5770,19 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1068225301421106</v>
+        <v>0.02569136511602165</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0.05348286136062599</v>
+        <v>-0.003176734367196341</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.007777985640169273</v>
+        <v>0.008306354570178641</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5794,22 +5794,22 @@
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.06069535207594721</v>
+        <v>-0.01041402143916544</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0.001524961702025594</v>
+        <v>0.004599817701949721</v>
       </c>
       <c r="CG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01151186270834415</v>
+        <v>0.003293275220866087</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
@@ -5824,19 +5824,19 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.001482830993595117</v>
+        <v>-0.01232954852818652</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.007052033586569641</v>
+        <v>0.004837041094238854</v>
       </c>
       <c r="CP10" t="n">
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.02131768151101869</v>
+        <v>0.003889678084678927</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5848,19 +5848,19 @@
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.05371793606610998</v>
+        <v>-0.008710158447955708</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0.01132481325843558</v>
+        <v>0.004139842018586787</v>
       </c>
       <c r="CY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.003377273385972071</v>
+        <v>0.001505979967022981</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5878,16 +5878,16 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.08139355921261715</v>
+        <v>-0.002249189649202658</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.006619849377195427</v>
+        <v>0.001903879323731754</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01789216067308341</v>
+        <v>-0.0003225901756561147</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
@@ -5902,22 +5902,22 @@
         <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.02272014966346853</v>
+        <v>-0.005968499046948017</v>
       </c>
       <c r="DP10" t="n">
-        <v>-0.02189740402408266</v>
+        <v>-0.002435878276476644</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.008298852607913847</v>
+        <v>0.006354376316889836</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5926,25 +5926,25 @@
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04566168274680538</v>
+        <v>0.008585289641145166</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.00706810877415196</v>
+        <v>0.004372524775456584</v>
       </c>
       <c r="DZ10" t="n">
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.02479005013971572</v>
+        <v>-0.007486628842582906</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -5956,22 +5956,22 @@
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.0358829171802196</v>
+        <v>-0.002675656358179613</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0.004232965610645155</v>
+        <v>0.000279133132326258</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01918994821063518</v>
+        <v>-7.180956237836324e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,28 +5980,28 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.03858774546355988</v>
+        <v>-0.009778810545461323</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01639303608941968</v>
+        <v>-0.001713186605839399</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02632513308216308</v>
+        <v>-0.001905863710572376</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>-0</v>
@@ -6010,19 +6010,19 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.05763519565337199</v>
+        <v>-0.01033676663999352</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0009798900049781865</v>
+        <v>0.004252394416053581</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.007362019531750552</v>
+        <v>0.0006124076264326299</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6040,52 +6040,52 @@
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01354034786126667</v>
+        <v>2.756605911939301e-06</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0.004584244658402126</v>
+        <v>0.007604178323643259</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.05004209334997105</v>
+        <v>-0.008320330902374188</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01688792866348733</v>
+        <v>-0.01568020699858865</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.002405189623050356</v>
+        <v>0.004908440146053468</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.03004644949887497</v>
+        <v>0.006864006044085836</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
@@ -6094,10 +6094,10 @@
         <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.006842757669304476</v>
+        <v>-0.008194057530854313</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0182250685541859</v>
+        <v>-0.00538091124962168</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,16 +6106,16 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>1.07655117473169</v>
+        <v>0.06987842786306772</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3086798434746027</v>
+        <v>-0.02319653508360515</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6144,40 +6144,40 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4235560973766549</v>
+        <v>-0.02358595728483119</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.036400284513878</v>
+        <v>0.1055576936492346</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4110648587723576</v>
+        <v>-0.04568295326680767</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.4873529932692863</v>
+        <v>-0.02773315206573499</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2614549252586887</v>
+        <v>0.02214312770023296</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,88 +6186,88 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.06915134355576935</v>
+        <v>-0.006569401747677139</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.1236215823576189</v>
+        <v>-0.004976910160365164</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2950079326844404</v>
+        <v>-0.02348792582253831</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.06882435304740453</v>
+        <v>-0.01983406981336124</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.02028011314576165</v>
+        <v>0.01428732105841432</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1950754887844166</v>
+        <v>0.02739289303877597</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.1080280091824102</v>
+        <v>0.01079206266493769</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.08862370585055197</v>
+        <v>-0.001822579202219732</v>
       </c>
       <c r="AT11" t="n">
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.8728329837670542</v>
+        <v>0.1154468428076384</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.03474776941333829</v>
+        <v>-0.01845411510681965</v>
       </c>
       <c r="AY11" t="n">
         <v>0</v>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.2446555010181081</v>
+        <v>0.001953751327134999</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.2105546880384907</v>
+        <v>-0.01087190922168239</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.3710953172947911</v>
+        <v>-0.0229426619393025</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,70 +6303,70 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0.1574209208962841</v>
+        <v>-0.02140514358609687</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.01018539332412521</v>
+        <v>0.006532437827409808</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.2630435967425576</v>
+        <v>0.03595828084655291</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.08892971843953804</v>
+        <v>0.02148566894722642</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.5593132126681714</v>
+        <v>0.0762464788383479</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0788562938299868</v>
+        <v>-0.01370817557106214</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0.1406673234879637</v>
+        <v>-0.01448956635481007</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.2530674407677443</v>
+        <v>-0.02975686804074287</v>
       </c>
       <c r="CF11" t="n">
         <v>-0</v>
@@ -6375,37 +6375,37 @@
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01072932733368561</v>
+        <v>0.01525226295788751</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.148943133604896</v>
+        <v>0.009819359622015007</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.09393112347189148</v>
+        <v>-0.05429527969335318</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1892133017572275</v>
+        <v>0.01867773667414724</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6414,52 +6414,52 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>-0.01531385003951432</v>
+        <v>0.005313061100425086</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.2411643179060456</v>
+        <v>-0.03082115130829143</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.007938295511548676</v>
+        <v>0.007281861708090988</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.1398352214110808</v>
+        <v>0.01001278696505972</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.4545801616029967</v>
+        <v>-0.03781884530078627</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04636374896488488</v>
+        <v>-0.006060309802771298</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,40 +6468,40 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.05308171628836977</v>
+        <v>0.002042889951778095</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.09070916330219875</v>
+        <v>-0.00760385312732717</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.05945343906870371</v>
+        <v>0.02183923280963283</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>-0.01160887075996165</v>
+        <v>0.0178308338495544</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1490376601790499</v>
+        <v>0.01644201451270427</v>
       </c>
       <c r="DY11" t="n">
         <v>-0</v>
@@ -6510,79 +6510,79 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.05130228632053894</v>
+        <v>0.01305682131729505</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.07214159646677706</v>
+        <v>0.01216436267644835</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1409818396831585</v>
+        <v>-0.01260392442386483</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.09278456132412632</v>
+        <v>-0.005435976666070668</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.1955597966981087</v>
+        <v>0.002646208543645472</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1684530159267517</v>
+        <v>-0.01594657047468724</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01765178961749953</v>
+        <v>0.004142748546500003</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.004094931281620931</v>
+        <v>0.01563275902302986</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.2689811229415634</v>
+        <v>-0.03318529161939063</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,52 +6591,52 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.01084386755103933</v>
+        <v>0.006557875457370165</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0992928193733887</v>
+        <v>0.009081573653252762</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.1445661915865358</v>
+        <v>-0.0290913800131174</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.1221173811937901</v>
+        <v>0.01609732064226558</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
         <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0560176252741455</v>
+        <v>0.01329212208656927</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.134385868947407</v>
+        <v>-0.06031949860703457</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,7 +6645,7 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.02780988679147212</v>
+        <v>0.006785946349358602</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
@@ -6657,34 +6657,34 @@
         <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.004584929642604728</v>
+        <v>0.005378525406797467</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.1875012614514844</v>
+        <v>-0.02773438357397304</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.07027262649948388</v>
+        <v>-0.01464745335188905</v>
       </c>
     </row>
     <row r="12">
@@ -7261,22 +7261,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6261803924183936</v>
+        <v>0.6603490376925959</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1825854731271223</v>
+        <v>-0.2911718685874024</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.151899930385779</v>
+        <v>0.005729288418927943</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7288,22 +7288,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.557644654889295</v>
+        <v>0.6965891089973413</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2213848202805021</v>
+        <v>-0.4248108861369903</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1812962960348681</v>
+        <v>-0.1099162731866786</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7312,73 +7312,73 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1861252416755048</v>
+        <v>0.152153797263066</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.02481254852484224</v>
+        <v>-0.06300567378115347</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06896576849497772</v>
+        <v>-0.1082858435138652</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1285244928419347</v>
+        <v>-0.04830220844953934</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.03126781349243794</v>
+        <v>-0.2626725161587437</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01425556062923818</v>
+        <v>-0.1638722979964662</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0772445216273171</v>
+        <v>0.2490588076005899</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.06234542869298786</v>
+        <v>-0.07873701489068485</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0476313685750106</v>
+        <v>0.08900329618295401</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -7396,25 +7396,25 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5043008356267583</v>
+        <v>0.5289645969350025</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0147828286004667</v>
+        <v>-0.1278333156934374</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1190402192324619</v>
+        <v>-0.3209665745830529</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
@@ -7423,25 +7423,25 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.05681340192052659</v>
+        <v>0.08487531154774865</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.07917561808799478</v>
+        <v>-0.04493665109178258</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.2616500914325233</v>
+        <v>0.03590676398705488</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,25 +7450,25 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.06062099069662588</v>
+        <v>-0.01777519963436141</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01901246541211337</v>
+        <v>-0.02659221544217034</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1073751005357653</v>
+        <v>0.0807429570893093</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
         <v>-0</v>
@@ -7477,49 +7477,49 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2823963506104176</v>
+        <v>0.470769714652873</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.02051636911950056</v>
+        <v>-0.1880130409110489</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08058884812704198</v>
+        <v>-0.07786451383861441</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1404122472651891</v>
+        <v>-0.1860630223782018</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.01360783165633929</v>
+        <v>0.1754513252232444</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01440113713808592</v>
+        <v>-0.002919314687820527</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,19 +7531,19 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02615539693281165</v>
+        <v>-0.2211420096926366</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.122279012128767</v>
+        <v>0.2379737949660689</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.141168730114605</v>
+        <v>0.0754654971881476</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,28 +7552,28 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1287627211523978</v>
+        <v>-0.1641606744403021</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03678187384537277</v>
+        <v>0.1792628093233581</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02787814999616012</v>
+        <v>-0.002039309265059522</v>
       </c>
       <c r="DA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
@@ -7585,22 +7585,22 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1559270204817975</v>
+        <v>-0.264268493380866</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.01290266319899928</v>
+        <v>0.02550713097014312</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06022319985600669</v>
+        <v>-0.05101175790165149</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7612,16 +7612,16 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.04647842107874928</v>
+        <v>-0.1324241640766298</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.1212982387613204</v>
+        <v>0.09318279948182455</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.06602869460348924</v>
+        <v>0.05803226045203114</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,85 +7630,85 @@
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0752989269575146</v>
+        <v>0.05281133754781365</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.01730004145329029</v>
+        <v>-0.02353652468855365</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.04536304700490228</v>
+        <v>-0.0571817805265937</v>
       </c>
       <c r="EB13" t="n">
         <v>0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.1057671570969245</v>
+        <v>-0.1520448919258092</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.05533669159353302</v>
+        <v>0.1736259781795643</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.08440512624115096</v>
+        <v>-0.02266329253393588</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1017813968770001</v>
+        <v>-0.06050435738300344</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.04291622385133612</v>
+        <v>0.06443258250381548</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.004511280516823347</v>
+        <v>-0.1124578560189324</v>
       </c>
       <c r="ET13" t="n">
         <v>-0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,46 +7717,46 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1296623773732693</v>
+        <v>-0.1985238526130476</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.03050017879692562</v>
+        <v>0.1817017918030444</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.02266434642411263</v>
+        <v>-0.01517203461826021</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02513710289130711</v>
+        <v>-0.1103060210601407</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.09319945374983706</v>
+        <v>0.1321475829493398</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.07270438323715497</v>
+        <v>-0.02436251764305943</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
@@ -7765,28 +7765,28 @@
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.05570247667777619</v>
+        <v>-0.2780579363694936</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.1120325463401922</v>
+        <v>0.1726477825511246</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.08286933677878591</v>
+        <v>0.1643660834338626</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,31 +7795,31 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.006122966368162621</v>
+        <v>-0.23884578361032</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.05933835224828725</v>
+        <v>0.1113905644209974</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,22 +7827,22 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8451868826014082</v>
+        <v>0.9395434724826714</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0882621056976996</v>
+        <v>0.01510624633380953</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5739532933246564</v>
+        <v>-0.5374565130779155</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7854,28 +7854,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7728615988011018</v>
+        <v>1.488823287966775</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01206163799122188</v>
+        <v>-0.35585725064729</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8044787128418242</v>
+        <v>-0.7331068712420448</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08655510995670869</v>
+        <v>0.2106304998301311</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1430076232963044</v>
+        <v>-0.1654675824387628</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.04688101038665704</v>
+        <v>-0.12465073969371</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.03272123756659236</v>
+        <v>-0.01997379246406274</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.03770838359999062</v>
+        <v>-0.5984857090814134</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01816391595661577</v>
+        <v>-0.1613062575269469</v>
       </c>
       <c r="AH14" t="n">
         <v>-0</v>
@@ -7932,13 +7932,13 @@
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.1436642376896963</v>
+        <v>0.0962369091833417</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -7947,13 +7947,13 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0597210136776365</v>
+        <v>-0.003969197404586585</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.1650827688659767</v>
+        <v>-0.06804119342751604</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.5887583211072606</v>
+        <v>1.297944300641292</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
@@ -7974,67 +7974,67 @@
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.03851613663963973</v>
+        <v>-0.248279794769924</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.4908728458206045</v>
+        <v>-0.5019397099316858</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.182014858793114</v>
+        <v>-0.05837705407375377</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.156599544266851</v>
+        <v>0.04005118601002956</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.1670659724797792</v>
+        <v>-0.02236635899760336</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1536979640607971</v>
+        <v>0.2390218442674076</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
         <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.01056406002501153</v>
+        <v>0.1261778764095085</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0.00309985185971515</v>
+        <v>0.02629331784644948</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8046,19 +8046,19 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.3284386011403767</v>
+        <v>0.7539120718256895</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.08564459704129353</v>
+        <v>-0.02675207116630683</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.2665645849447539</v>
+        <v>-0.2945572284381956</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8073,7 +8073,7 @@
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1450761932908145</v>
+        <v>-0.2854940462180966</v>
       </c>
       <c r="CF14" t="n">
         <v>0</v>
@@ -8082,40 +8082,40 @@
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02990799635033625</v>
+        <v>0.02416352893218396</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.1292040192821824</v>
+        <v>0.2038750320938785</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.006738650565011725</v>
+        <v>-0.5193744373068454</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.00510745855288866</v>
+        <v>-0.02199348858774867</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0393390589541948</v>
+        <v>0.07705739849136763</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>-0</v>
@@ -8124,49 +8124,49 @@
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1263452339924312</v>
+        <v>-0.3040816467167325</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.04635676313363981</v>
+        <v>-0.005539097697534221</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.1572882544961943</v>
+        <v>0.2362466735716112</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.04369269658903357</v>
+        <v>-0.1411708683892746</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08787767673841698</v>
+        <v>-0.3577711889672212</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.02111243539704888</v>
+        <v>0.1267296183663088</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8178,22 +8178,22 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.001692738875101384</v>
+        <v>-0.2181919975238027</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.005619541001832222</v>
+        <v>0.141889634623192</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.006675520764634889</v>
+        <v>0.136002651334731</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
@@ -8202,79 +8202,79 @@
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.1050841313892098</v>
+        <v>-0.2295827165174238</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01645632860582909</v>
+        <v>0.0585600747174228</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.07103768397696478</v>
+        <v>-0.2759962505495742</v>
       </c>
       <c r="EC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.147816347616805</v>
+        <v>0.006929092100287114</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
         <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.007524953715021591</v>
+        <v>-0.1478641648661111</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.137889646258002</v>
+        <v>0.07949251387453668</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.04264838286221744</v>
+        <v>-0.03733484386572444</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.02229942141410714</v>
+        <v>-0.1122034074768832</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.04797659531792799</v>
+        <v>0.05833694649994979</v>
       </c>
       <c r="EU14" t="n">
         <v>-0</v>
@@ -8283,13 +8283,13 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.119811124933045</v>
+        <v>-0.3413911935752838</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
@@ -8298,52 +8298,52 @@
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.04019032015589614</v>
+        <v>-0.04461209386087346</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.1272420192519838</v>
+        <v>0.2172789767407362</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.04552475122869735</v>
+        <v>0.2111453752465035</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.006282128833498454</v>
+        <v>0.02836086982368369</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.128450045690679</v>
+        <v>0.07881934299558845</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.08047951084102489</v>
+        <v>-0.1282694926802107</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,54 +8352,54 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.1439576643159495</v>
+        <v>0.1141500704204354</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0435041625993477</v>
+        <v>-0.002061052664398326</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.05311795689890232</v>
+        <v>-0.02039404147146701</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.1132097139190412</v>
+        <v>0.0552976975317168</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.06014025353990304</v>
+        <v>-0.06834718101212237</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7559160751868513</v>
+        <v>0.236018382111486</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06985144059542645</v>
+        <v>-0.1635165087845168</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8417,16 +8417,16 @@
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.09770725450191127</v>
+        <v>-0.06467056952726881</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6483257000115195</v>
+        <v>0.3463675271713407</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1188037613568113</v>
+        <v>-0.2336904915435957</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8450,19 +8450,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02969155851460921</v>
+        <v>0.0291571985404377</v>
       </c>
       <c r="T15" t="n">
-        <v>0.174001496076779</v>
+        <v>0.07654158240874491</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1142436788204044</v>
+        <v>0.01204169377069052</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
@@ -8471,16 +8471,16 @@
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05458632349184174</v>
+        <v>-0.02130312369993509</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1890378496741431</v>
+        <v>0.01074093682453625</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
@@ -8489,10 +8489,10 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01726965515030805</v>
+        <v>-0.1103947824964584</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8504,64 +8504,64 @@
         <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.01968110382001605</v>
+        <v>-0.04534082306647706</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.08381647909148353</v>
+        <v>0.03609800520015991</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.03594492668424257</v>
+        <v>-0.03484637678518467</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.01433318026376884</v>
+        <v>-0.03675330571036327</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5388565651964593</v>
+        <v>0.3110676261836113</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.2733207995688589</v>
+        <v>-0.174534920749869</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0.03262242586781026</v>
+        <v>-0.03810364251224994</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.09246218289384246</v>
+        <v>0.02706694393287787</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2418740209685584</v>
+        <v>-0.04365364019014956</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -8579,16 +8579,16 @@
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.01788374426379456</v>
+        <v>0.01787785604294703</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.01577599878354496</v>
+        <v>0.1024213015965714</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
@@ -8597,13 +8597,13 @@
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.06500415498358138</v>
+        <v>0.1141724241533458</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8612,19 +8612,19 @@
         <v>-0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.02559144287264304</v>
+        <v>0.02112480177378851</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.3198006119006951</v>
+        <v>0.1855471292384643</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08895399739680455</v>
+        <v>-0.0334570967575683</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,85 +8633,85 @@
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.01012665424641275</v>
+        <v>0.03733202246081634</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1516447827113718</v>
+        <v>-0.05172263899352641</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.02416613536352152</v>
+        <v>0.07234970675362268</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0.06182979534064348</v>
+        <v>-0.04202455676512683</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.02407588590297823</v>
+        <v>-0.1744707449033273</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1953118994374817</v>
+        <v>0.01697448260884862</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0.002362991336976019</v>
+        <v>0.01545438224324665</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.148335936510134</v>
+        <v>-0.04700188811741141</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.03805179334552113</v>
+        <v>0.03636474944926273</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>0</v>
@@ -8720,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>-0.02332444610622687</v>
+        <v>0.009719528430759189</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.2200930114090549</v>
+        <v>-0.1167650814168895</v>
       </c>
       <c r="DG15" t="n">
         <v>-0</v>
@@ -8732,13 +8732,13 @@
         <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.03763598134658636</v>
+        <v>-0.1057697140234398</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
@@ -8747,49 +8747,49 @@
         <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0.02938999004562641</v>
+        <v>-0.002499648443248986</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.09007145773977901</v>
+        <v>0.006966989309022689</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
         <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.0183741855295424</v>
+        <v>-0.004652812548151025</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0.01668332801591736</v>
+        <v>0.08303990538664555</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0884334672656685</v>
+        <v>-0.06360959323842719</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.06112718932960921</v>
+        <v>-0.05586089066107171</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8801,25 +8801,25 @@
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0.06885659400973951</v>
+        <v>-0.05495552563130503</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1026744791034596</v>
+        <v>-0.00443471560286781</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.03086503339790756</v>
+        <v>0.0295258361741499</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,37 +8828,37 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0.0292500636633811</v>
+        <v>-0.02475297278022199</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.1170861840271164</v>
+        <v>0.0325482169143736</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.09906244937961431</v>
+        <v>-0.01017383398940294</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>-0.01843949363872488</v>
+        <v>0.03305538607001281</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.153271972198459</v>
+        <v>-0.07981410276284337</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
@@ -8867,25 +8867,25 @@
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.0640207907578746</v>
+        <v>0.0427219185381893</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0.02366564188246518</v>
+        <v>-0.01318782859691913</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.003586562309781532</v>
+        <v>0.06956980434581068</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,7 +8894,7 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.03113941485492434</v>
+        <v>-0.1077070231257792</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8906,13 +8906,13 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0.06204241689799877</v>
+        <v>0.01134203871886512</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.1034466027211123</v>
+        <v>-0.07805935079048769</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,37 +8921,37 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.09857380443985397</v>
+        <v>0.1724650764419493</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0.08101283160317227</v>
+        <v>0.02442858515729589</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.08862176314892406</v>
+        <v>-0.06087656303684617</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,16 +8968,16 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.496108812510229</v>
+        <v>0.05974302552426958</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2138413914503496</v>
+        <v>-0.01494174788889323</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8986,7 +8986,7 @@
         <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01160515399787728</v>
+        <v>-0.008711548848316703</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,34 +8995,34 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3706495961233287</v>
+        <v>0.07544198059716939</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2092583061511894</v>
+        <v>-0.03613541289046729</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.07648810788315069</v>
+        <v>-0.02470214200802067</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.09636474354702862</v>
+        <v>0.00714903851393022</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,16 +9031,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02368354983952369</v>
+        <v>0.00414149490191196</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.04127219074552031</v>
+        <v>0.00180621030260174</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -9049,34 +9049,34 @@
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1666919029269363</v>
+        <v>-0.0002279702473367576</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.102178188557609</v>
+        <v>-0.01736379658426689</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0005976743956571907</v>
+        <v>-0.0015352227926981</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.07169456335808404</v>
+        <v>0.01234930765111018</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
@@ -9085,25 +9085,25 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.01630278975200185</v>
+        <v>0.00719597262161656</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.05176510460015871</v>
+        <v>-0.00111673167811038</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.3600997389792789</v>
+        <v>0.04645831225380382</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,7 +9112,7 @@
         <v>-0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.03971385671460051</v>
+        <v>0.005545188590541761</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9121,16 +9121,16 @@
         <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.04807782622412105</v>
+        <v>-0.007011170985185272</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0566557062371889</v>
+        <v>-0.00168878134624734</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,16 +9139,16 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1721571829961126</v>
+        <v>-0.0166335466017207</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-0.05488902876465854</v>
+        <v>-0.0004876500916649899</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.05807176288054505</v>
+        <v>-0.003650678459864865</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
@@ -9166,43 +9166,43 @@
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.07178497128385507</v>
+        <v>0.02448813696120251</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.01226772561921159</v>
+        <v>0.01323881732945643</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.2149986428488955</v>
+        <v>0.03213513507526792</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01575314329826755</v>
+        <v>0.01167646047888003</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.03268531855020936</v>
+        <v>-0.002037923342297172</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -9211,16 +9211,16 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.08899839559882984</v>
+        <v>-0.01912193469610118</v>
       </c>
       <c r="CF16" t="n">
         <v>0</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.02234642038437936</v>
+        <v>0.004065894738428055</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
@@ -9229,79 +9229,79 @@
         <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0.005959442439026973</v>
+        <v>0.005082679366561415</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.03579101783991353</v>
+        <v>-0.02575169116245343</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.1589194909378188</v>
+        <v>-0.009418940360596879</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0.007811517471522356</v>
+        <v>0.002429671315919958</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.07836253424179268</v>
+        <v>-0.0191753602772745</v>
       </c>
       <c r="CX16" t="n">
         <v>-0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.006052390508619456</v>
+        <v>0.003558876079412065</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
-        <v>-0.0162915523069824</v>
+        <v>0.006570368535626179</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.1591609430248629</v>
+        <v>-0.01363031670897832</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08467995681429141</v>
+        <v>-0.006708928318779451</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9310,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0.04877164712764352</v>
+        <v>-0.005073009034741768</v>
       </c>
       <c r="DM16" t="n">
         <v>-0</v>
@@ -9319,7 +9319,7 @@
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.003497011998754873</v>
+        <v>-0.004551345733329054</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
@@ -9328,7 +9328,7 @@
         <v>-0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.04526628662210549</v>
+        <v>-0.001422783632162132</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
@@ -9337,43 +9337,43 @@
         <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>-0.008616036688694892</v>
+        <v>0.01043967689858488</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.04383267715819726</v>
+        <v>-0.01292125762987624</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06274248645006321</v>
+        <v>-0.003090067460209331</v>
       </c>
       <c r="EB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.03288770801504568</v>
+        <v>-0.004233256973399555</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.06972229292031701</v>
+        <v>-0.002681365679212579</v>
       </c>
       <c r="EH16" t="n">
         <v>0</v>
@@ -9382,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.06515017423860131</v>
+        <v>-0.001909715600685276</v>
       </c>
       <c r="EK16" t="n">
         <v>-0</v>
@@ -9391,52 +9391,52 @@
         <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0.03009901638732109</v>
+        <v>0.003377355014444841</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.04591140526692313</v>
+        <v>-0.01647638207102562</v>
       </c>
       <c r="EQ16" t="n">
         <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.009854573468013944</v>
+        <v>-0.0004139498491432637</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0.006327445682362872</v>
+        <v>0.004597956565378714</v>
       </c>
       <c r="EW16" t="n">
         <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.07916989665247526</v>
+        <v>-0.02057153628990373</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.00974748109610697</v>
+        <v>-0.0007744115711270816</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
@@ -9445,16 +9445,16 @@
         <v>-0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0.004404987802374612</v>
+        <v>0.004307197978145548</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.04574016003697361</v>
+        <v>0.0109601981137079</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.04944482058672442</v>
+        <v>-0.006686389215684092</v>
       </c>
       <c r="FL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.01350596772321621</v>
+        <v>0.001067179156090278</v>
       </c>
       <c r="FO16" t="n">
         <v>-0</v>
@@ -9481,7 +9481,7 @@
         <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.004139692318313632</v>
+        <v>-0.004069766829073748</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,25 +9490,25 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.04997407532098021</v>
+        <v>-0.001359874963627419</v>
       </c>
       <c r="FU16" t="n">
         <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.001998931832472726</v>
+        <v>0.001927024887806021</v>
       </c>
       <c r="FX16" t="n">
         <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.06073332036277141</v>
+        <v>-0.01315697925525927</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9520,16 +9520,16 @@
         <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0.05771619450676856</v>
+        <v>-0.01220221451096945</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
